--- a/data/supervison.xlsx
+++ b/data/supervison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conorisco/Dropbox (Personal)/Jobs/CV and Publications/CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4497F62-501F-5145-A49C-28D8F9196CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62382D43-E090-5643-B730-61FBA0FEA8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14460" yWindow="6560" windowWidth="29520" windowHeight="18200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4520" yWindow="5880" windowWidth="29520" windowHeight="18200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
   <si>
     <t>with</t>
   </si>
@@ -267,6 +267,24 @@
   </si>
   <si>
     <t>Linda Romano</t>
+  </si>
+  <si>
+    <t>Redacted</t>
+  </si>
+  <si>
+    <t>MSc Molecular Medicine</t>
+  </si>
+  <si>
+    <t>Medicine (Summer scholarship)</t>
+  </si>
+  <si>
+    <t>Technological University of Dublin</t>
+  </si>
+  <si>
+    <t>Bartosz Urban</t>
+  </si>
+  <si>
+    <t>Biomedical &amp; Molecular Diagnostics (Placment)</t>
   </si>
 </sst>
 </file>
@@ -634,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
@@ -1039,6 +1057,62 @@
         <v>19</v>
       </c>
     </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25">
+        <v>2026</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26">
+        <v>2026</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27">
+        <v>2026</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28">
+        <v>2026</v>
+      </c>
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
